--- a/JP (Exclude Game)/Data/chara_talk.xlsx
+++ b/JP (Exclude Game)/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$136</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$137</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="323">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -158,6 +158,15 @@
 ﾋﾟｷﾞｬｧｧｧ
 ﾋﾟｷﾞｬｱｱｱｧｧｧ
 ﾋﾟ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fusion2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エンタングル！
+せーのっ！
+ぎゅーっ！
+集合～！</t>
   </si>
   <si>
     <t xml:space="preserve">play_baby</t>
@@ -1907,9 +1916,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2079360</xdr:colOff>
+      <xdr:colOff>2079000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>123480</xdr:rowOff>
+      <xdr:rowOff>123120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1919,7 +1928,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50979960" cy="123480"/>
+          <a:ext cx="50979600" cy="123120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1952,9 +1961,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>516960</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>315720</xdr:rowOff>
+      <xdr:colOff>516600</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>315360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1964,7 +1973,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55188000" cy="46602000"/>
+          <a:ext cx="55187640" cy="47151000"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -2099,7 +2108,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CJ137"/>
+  <dimension ref="A1:CJ138"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2405,7 +2414,7 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -2441,7 +2450,7 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -2477,11 +2486,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>48</v>
       </c>
       <c r="U8" s="3"/>
@@ -2513,11 +2522,11 @@
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>50</v>
       </c>
       <c r="U9" s="3"/>
@@ -2549,7 +2558,7 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
@@ -2585,11 +2594,11 @@
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>54</v>
       </c>
       <c r="U11" s="3"/>
@@ -2693,11 +2702,11 @@
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="1" t="s">
         <v>60</v>
       </c>
       <c r="U14" s="3"/>
@@ -2729,7 +2738,7 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
@@ -2765,7 +2774,7 @@
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>63</v>
       </c>
@@ -2801,7 +2810,7 @@
       <c r="AU16" s="3"/>
       <c r="AV16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -2873,7 +2882,7 @@
       <c r="AU18" s="3"/>
       <c r="AV18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -2909,7 +2918,7 @@
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
@@ -2945,7 +2954,7 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -2981,7 +2990,7 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>75</v>
       </c>
@@ -3017,7 +3026,7 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>77</v>
       </c>
@@ -3053,8 +3062,8 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -3089,14 +3098,13 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="4"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -3126,13 +3134,14 @@
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>84</v>
       </c>
+      <c r="C26" s="4"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3163,13 +3172,12 @@
       <c r="AV26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="4"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3207,7 +3215,6 @@
         <v>88</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -3237,7 +3244,7 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>89</v>
       </c>
@@ -3275,7 +3282,7 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
@@ -3313,7 +3320,7 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>93</v>
       </c>
@@ -3321,6 +3328,7 @@
         <v>94</v>
       </c>
       <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3350,7 +3358,7 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>95</v>
       </c>
@@ -3387,13 +3395,14 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="C33" s="4"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3423,7 +3432,7 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>99</v>
       </c>
@@ -3459,15 +3468,13 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3497,13 +3504,15 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>104</v>
       </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3533,11 +3542,11 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="4" t="s">
         <v>106</v>
       </c>
       <c r="U37" s="3"/>
@@ -3569,14 +3578,13 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="4"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3606,8 +3614,8 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+    <row r="39" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
         <v>109</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -3643,14 +3651,14 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3680,14 +3688,14 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3717,14 +3725,14 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E42" s="4"/>
+      <c r="C42" s="4"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3754,13 +3762,14 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>118</v>
       </c>
+      <c r="E43" s="4"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -3790,7 +3799,7 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>119</v>
       </c>
@@ -3826,7 +3835,7 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
@@ -3862,7 +3871,7 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
@@ -3898,7 +3907,7 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>125</v>
       </c>
@@ -3934,15 +3943,13 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -3972,7 +3979,7 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -4010,14 +4017,15 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4047,13 +4055,14 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>134</v>
       </c>
+      <c r="F51" s="4"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4155,11 +4164,11 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="4" t="s">
         <v>140</v>
       </c>
       <c r="U54" s="3"/>
@@ -4191,11 +4200,11 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
       <c r="U55" s="3"/>
@@ -4227,7 +4236,7 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>143</v>
       </c>
@@ -4263,7 +4272,7 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>145</v>
       </c>
@@ -4299,7 +4308,7 @@
       <c r="AU57" s="3"/>
       <c r="AV57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>147</v>
       </c>
@@ -4336,30 +4345,12 @@
       <c r="AV58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6"/>
-      <c r="S59" s="6"/>
-      <c r="T59" s="6"/>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -4389,11 +4380,11 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>152</v>
       </c>
       <c r="C60" s="6"/>
@@ -4443,11 +4434,11 @@
       <c r="AU60" s="3"/>
       <c r="AV60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="6" t="s">
         <v>154</v>
       </c>
       <c r="C61" s="6"/>
@@ -4497,13 +4488,31 @@
       <c r="AU61" s="3"/>
       <c r="AV61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+    <row r="62" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="4" t="s">
         <v>156</v>
       </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
@@ -4641,11 +4650,11 @@
       <c r="AU65" s="3"/>
       <c r="AV65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="1" t="s">
         <v>164</v>
       </c>
       <c r="U66" s="3"/>
@@ -4677,7 +4686,7 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>165</v>
       </c>
@@ -4713,11 +4722,11 @@
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="4" t="s">
         <v>168</v>
       </c>
       <c r="U68" s="3"/>
@@ -4749,11 +4758,11 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="1" t="s">
         <v>170</v>
       </c>
       <c r="U69" s="3"/>
@@ -4785,11 +4794,11 @@
       <c r="AU69" s="3"/>
       <c r="AV69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="4" t="s">
         <v>172</v>
       </c>
       <c r="U70" s="3"/>
@@ -4893,11 +4902,11 @@
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="1" t="s">
         <v>178</v>
       </c>
       <c r="U73" s="3"/>
@@ -4929,9 +4938,12 @@
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>179</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>180</v>
       </c>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
@@ -4962,11 +4974,8 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B75" s="4" t="s">
         <v>181</v>
       </c>
       <c r="U75" s="3"/>
@@ -4998,11 +5007,11 @@
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="4" t="s">
         <v>183</v>
       </c>
       <c r="U76" s="3"/>
@@ -5034,12 +5043,12 @@
       <c r="AU76" s="3"/>
       <c r="AV76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>164</v>
+      <c r="B77" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
@@ -5070,12 +5079,12 @@
       <c r="AU77" s="3"/>
       <c r="AV77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B78" s="1" t="s">
         <v>186</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
@@ -5106,11 +5115,11 @@
       <c r="AU78" s="3"/>
       <c r="AV78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="1" t="s">
         <v>188</v>
       </c>
       <c r="U79" s="3"/>
@@ -5142,7 +5151,7 @@
       <c r="AU79" s="3"/>
       <c r="AV79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>189</v>
       </c>
@@ -5178,7 +5187,7 @@
       <c r="AU80" s="3"/>
       <c r="AV80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>191</v>
       </c>
@@ -5214,7 +5223,7 @@
       <c r="AU81" s="3"/>
       <c r="AV81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
@@ -5250,7 +5259,7 @@
       <c r="AU82" s="3"/>
       <c r="AV82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>195</v>
       </c>
@@ -5286,11 +5295,11 @@
       <c r="AU83" s="3"/>
       <c r="AV83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="4" t="s">
         <v>198</v>
       </c>
       <c r="U84" s="3"/>
@@ -5322,11 +5331,11 @@
       <c r="AU84" s="3"/>
       <c r="AV84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="1" t="s">
         <v>200</v>
       </c>
       <c r="U85" s="3"/>
@@ -5358,7 +5367,7 @@
       <c r="AU85" s="3"/>
       <c r="AV85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>201</v>
       </c>
@@ -5394,11 +5403,11 @@
       <c r="AU86" s="3"/>
       <c r="AV86" s="3"/>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="4" t="s">
         <v>204</v>
       </c>
       <c r="U87" s="3"/>
@@ -5502,7 +5511,7 @@
       <c r="AU89" s="3"/>
       <c r="AV89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>209</v>
       </c>
@@ -5538,7 +5547,7 @@
       <c r="AU90" s="3"/>
       <c r="AV90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
         <v>211</v>
       </c>
@@ -5574,11 +5583,11 @@
       <c r="AU91" s="3"/>
       <c r="AV91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="1" t="s">
         <v>214</v>
       </c>
       <c r="U92" s="3"/>
@@ -5610,11 +5619,11 @@
       <c r="AU92" s="3"/>
       <c r="AV92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="4" t="s">
         <v>216</v>
       </c>
       <c r="U93" s="3"/>
@@ -5646,11 +5655,11 @@
       <c r="AU93" s="3"/>
       <c r="AV93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="1" t="s">
         <v>218</v>
       </c>
       <c r="U94" s="3"/>
@@ -5682,13 +5691,41 @@
       <c r="AU94" s="3"/>
       <c r="AV94" s="3"/>
     </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="4" t="s">
         <v>220</v>
       </c>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
+      <c r="AS95" s="3"/>
+      <c r="AT95" s="3"/>
+      <c r="AU95" s="3"/>
+      <c r="AV95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
@@ -5702,16 +5739,16 @@
       <c r="A97" s="1" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B98" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
         <v>226</v>
       </c>
@@ -5719,7 +5756,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>228</v>
       </c>
@@ -5727,39 +5764,39 @@
         <v>229</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
+    <row r="101" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
-      <c r="N101" s="6"/>
-      <c r="O101" s="6"/>
-      <c r="P101" s="6"/>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6"/>
-      <c r="S101" s="6"/>
-      <c r="T101" s="6"/>
-    </row>
-    <row r="102" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+    </row>
+    <row r="102" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="6" t="s">
         <v>232</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>233</v>
       </c>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+      <c r="N102" s="6"/>
+      <c r="O102" s="6"/>
+      <c r="P102" s="6"/>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6"/>
     </row>
     <row r="103" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
@@ -5769,7 +5806,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>236</v>
       </c>
@@ -5777,7 +5814,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
         <v>238</v>
       </c>
@@ -5785,7 +5822,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>240</v>
       </c>
@@ -5793,7 +5830,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>242</v>
       </c>
@@ -5801,93 +5838,93 @@
         <v>243</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6" t="s">
+    <row r="108" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
         <v>244</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
-      <c r="N108" s="6"/>
-      <c r="O108" s="6"/>
-      <c r="P108" s="6"/>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-    </row>
-    <row r="109" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="s">
         <v>246</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="4"/>
-      <c r="L109" s="4"/>
-      <c r="M109" s="4"/>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
-      <c r="Q109" s="4"/>
-      <c r="R109" s="4"/>
-      <c r="S109" s="4"/>
-      <c r="T109" s="4"/>
-    </row>
-    <row r="110" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6" t="s">
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+      <c r="N109" s="6"/>
+      <c r="O109" s="6"/>
+      <c r="P109" s="6"/>
+      <c r="Q109" s="6"/>
+      <c r="R109" s="6"/>
+      <c r="S109" s="6"/>
+      <c r="T109" s="6"/>
+    </row>
+    <row r="110" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="s">
         <v>248</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
-      <c r="N110" s="6"/>
-      <c r="O110" s="6"/>
-      <c r="P110" s="6"/>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-    </row>
-    <row r="111" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+      <c r="S110" s="4"/>
+      <c r="T110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="6" t="s">
         <v>250</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="6"/>
+      <c r="O111" s="6"/>
+      <c r="P111" s="6"/>
+      <c r="Q111" s="6"/>
+      <c r="R111" s="6"/>
+      <c r="S111" s="6"/>
+      <c r="T111" s="6"/>
+    </row>
+    <row r="112" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>252</v>
       </c>
@@ -5895,7 +5932,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>254</v>
       </c>
@@ -5903,31 +5940,13 @@
         <v>255</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="6" t="s">
+    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
         <v>256</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
-      <c r="M114" s="6"/>
-      <c r="N114" s="6"/>
-      <c r="O114" s="6"/>
-      <c r="P114" s="6"/>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
@@ -5955,77 +5974,95 @@
       <c r="S115" s="6"/>
       <c r="T115" s="6"/>
     </row>
-    <row r="116" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+    <row r="116" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="6" t="s">
         <v>260</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
+      <c r="N116" s="6"/>
+      <c r="O116" s="6"/>
+      <c r="P116" s="6"/>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6"/>
+      <c r="T116" s="6"/>
+    </row>
+    <row r="117" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="B117" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="C117" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="D117" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="E117" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="H116" s="4" t="s">
+      <c r="F117" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="I116" s="4" t="s">
+      <c r="G117" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J116" s="4" t="s">
+      <c r="H117" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="K116" s="4" t="s">
+      <c r="I117" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="L116" s="4" t="s">
+      <c r="J117" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="M116" s="4" t="s">
+      <c r="K117" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="N116" s="4" t="s">
+      <c r="L117" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="O116" s="4" t="s">
+      <c r="M117" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="P116" s="4" t="s">
+      <c r="N117" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="Q116" s="4" t="s">
+      <c r="O117" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="R116" s="4" t="s">
+      <c r="P117" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="S116" s="4" t="s">
+      <c r="Q117" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="T116" s="4" t="s">
+      <c r="R117" s="4" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+      <c r="S117" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="T117" s="4" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>282</v>
       </c>
@@ -6033,41 +6070,41 @@
         <v>283</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6" t="s">
+    <row r="119" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
-      <c r="M119" s="6"/>
-      <c r="N119" s="6"/>
-      <c r="O119" s="6"/>
-      <c r="P119" s="6"/>
-      <c r="Q119" s="6"/>
-      <c r="R119" s="6"/>
-      <c r="S119" s="6"/>
-      <c r="T119" s="6"/>
-    </row>
-    <row r="120" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+    </row>
+    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="B120" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="6"/>
+      <c r="K120" s="6"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="6"/>
+      <c r="O120" s="6"/>
+      <c r="P120" s="6"/>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+    </row>
+    <row r="121" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>288</v>
       </c>
@@ -6075,85 +6112,85 @@
         <v>289</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="7" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="L123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="M123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="N123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="P123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="R123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="T123" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="P124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="S124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="T124" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>296</v>
       </c>
@@ -6161,11 +6198,11 @@
         <v>297</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="4" t="s">
         <v>299</v>
       </c>
     </row>
@@ -6177,68 +6214,68 @@
         <v>301</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>304</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="AX129" s="3"/>
-      <c r="AY129" s="3"/>
-      <c r="AZ129" s="3"/>
-      <c r="BA129" s="3"/>
-      <c r="BB129" s="3"/>
-      <c r="BC129" s="3"/>
-      <c r="BD129" s="3"/>
-      <c r="BE129" s="3"/>
-      <c r="BF129" s="3"/>
-      <c r="BG129" s="3"/>
-      <c r="BH129" s="3"/>
-      <c r="BI129" s="3"/>
-      <c r="BJ129" s="3"/>
-      <c r="BK129" s="3"/>
-      <c r="BL129" s="3"/>
-      <c r="BM129" s="3"/>
-      <c r="BN129" s="3"/>
-      <c r="BO129" s="3"/>
-      <c r="BP129" s="3"/>
-      <c r="BQ129" s="3"/>
-      <c r="BR129" s="3"/>
-      <c r="BS129" s="3"/>
-      <c r="BT129" s="3"/>
-      <c r="BU129" s="3"/>
-      <c r="BV129" s="3"/>
-      <c r="BW129" s="3"/>
-      <c r="BX129" s="3"/>
-      <c r="BY129" s="3"/>
-      <c r="BZ129" s="3"/>
-      <c r="CA129" s="3"/>
-      <c r="CB129" s="3"/>
-      <c r="CC129" s="3"/>
-      <c r="CD129" s="3"/>
-      <c r="CE129" s="3"/>
-      <c r="CF129" s="3"/>
-      <c r="CG129" s="3"/>
-      <c r="CH129" s="3"/>
-      <c r="CI129" s="3"/>
-      <c r="CJ129" s="3"/>
-    </row>
-    <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
         <v>306</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>307</v>
       </c>
+      <c r="AX130" s="3"/>
+      <c r="AY130" s="3"/>
+      <c r="AZ130" s="3"/>
+      <c r="BA130" s="3"/>
+      <c r="BB130" s="3"/>
+      <c r="BC130" s="3"/>
+      <c r="BD130" s="3"/>
+      <c r="BE130" s="3"/>
+      <c r="BF130" s="3"/>
+      <c r="BG130" s="3"/>
+      <c r="BH130" s="3"/>
+      <c r="BI130" s="3"/>
+      <c r="BJ130" s="3"/>
+      <c r="BK130" s="3"/>
+      <c r="BL130" s="3"/>
+      <c r="BM130" s="3"/>
+      <c r="BN130" s="3"/>
+      <c r="BO130" s="3"/>
+      <c r="BP130" s="3"/>
+      <c r="BQ130" s="3"/>
+      <c r="BR130" s="3"/>
+      <c r="BS130" s="3"/>
+      <c r="BT130" s="3"/>
+      <c r="BU130" s="3"/>
+      <c r="BV130" s="3"/>
+      <c r="BW130" s="3"/>
+      <c r="BX130" s="3"/>
+      <c r="BY130" s="3"/>
+      <c r="BZ130" s="3"/>
+      <c r="CA130" s="3"/>
+      <c r="CB130" s="3"/>
+      <c r="CC130" s="3"/>
+      <c r="CD130" s="3"/>
+      <c r="CE130" s="3"/>
+      <c r="CF130" s="3"/>
+      <c r="CG130" s="3"/>
+      <c r="CH130" s="3"/>
+      <c r="CI130" s="3"/>
+      <c r="CJ130" s="3"/>
     </row>
     <row r="131" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
@@ -6247,47 +6284,8 @@
       <c r="B131" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="AX131" s="3"/>
-      <c r="AY131" s="3"/>
-      <c r="AZ131" s="3"/>
-      <c r="BA131" s="3"/>
-      <c r="BB131" s="3"/>
-      <c r="BC131" s="3"/>
-      <c r="BD131" s="3"/>
-      <c r="BE131" s="3"/>
-      <c r="BF131" s="3"/>
-      <c r="BG131" s="3"/>
-      <c r="BH131" s="3"/>
-      <c r="BI131" s="3"/>
-      <c r="BJ131" s="3"/>
-      <c r="BK131" s="3"/>
-      <c r="BL131" s="3"/>
-      <c r="BM131" s="3"/>
-      <c r="BN131" s="3"/>
-      <c r="BO131" s="3"/>
-      <c r="BP131" s="3"/>
-      <c r="BQ131" s="3"/>
-      <c r="BR131" s="3"/>
-      <c r="BS131" s="3"/>
-      <c r="BT131" s="3"/>
-      <c r="BU131" s="3"/>
-      <c r="BV131" s="3"/>
-      <c r="BW131" s="3"/>
-      <c r="BX131" s="3"/>
-      <c r="BY131" s="3"/>
-      <c r="BZ131" s="3"/>
-      <c r="CA131" s="3"/>
-      <c r="CB131" s="3"/>
-      <c r="CC131" s="3"/>
-      <c r="CD131" s="3"/>
-      <c r="CE131" s="3"/>
-      <c r="CF131" s="3"/>
-      <c r="CG131" s="3"/>
-      <c r="CH131" s="3"/>
-      <c r="CI131" s="3"/>
-      <c r="CJ131" s="3"/>
-    </row>
-    <row r="132" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="132" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>310</v>
       </c>
@@ -6334,78 +6332,117 @@
       <c r="CI132" s="3"/>
       <c r="CJ132" s="3"/>
     </row>
-    <row r="133" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>312</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
-      <c r="G133" s="1"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
-      <c r="K133" s="1"/>
-      <c r="L133" s="1"/>
-      <c r="M133" s="1"/>
-      <c r="N133" s="1"/>
-      <c r="O133" s="1"/>
-      <c r="P133" s="1"/>
-      <c r="Q133" s="1"/>
-      <c r="R133" s="1"/>
-      <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
-      <c r="U133" s="1"/>
-      <c r="V133" s="1"/>
-      <c r="W133" s="1"/>
-      <c r="X133" s="1"/>
-      <c r="Y133" s="1"/>
-      <c r="Z133" s="1"/>
-      <c r="AA133" s="1"/>
-      <c r="AB133" s="1"/>
-      <c r="AC133" s="1"/>
-      <c r="AD133" s="1"/>
-      <c r="AE133" s="1"/>
-      <c r="AF133" s="1"/>
-      <c r="AG133" s="1"/>
-      <c r="AH133" s="1"/>
-      <c r="AI133" s="1"/>
-      <c r="AJ133" s="1"/>
-      <c r="AK133" s="1"/>
-      <c r="AL133" s="1"/>
-      <c r="AM133" s="1"/>
-      <c r="AN133" s="1"/>
-      <c r="AO133" s="1"/>
-      <c r="AP133" s="1"/>
-      <c r="AQ133" s="1"/>
-      <c r="AR133" s="1"/>
-      <c r="AS133" s="1"/>
-      <c r="AT133" s="1"/>
-      <c r="AU133" s="1"/>
-      <c r="AV133" s="1"/>
-      <c r="AW133" s="1"/>
-    </row>
-    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>313</v>
+      </c>
+      <c r="AX133" s="3"/>
+      <c r="AY133" s="3"/>
+      <c r="AZ133" s="3"/>
+      <c r="BA133" s="3"/>
+      <c r="BB133" s="3"/>
+      <c r="BC133" s="3"/>
+      <c r="BD133" s="3"/>
+      <c r="BE133" s="3"/>
+      <c r="BF133" s="3"/>
+      <c r="BG133" s="3"/>
+      <c r="BH133" s="3"/>
+      <c r="BI133" s="3"/>
+      <c r="BJ133" s="3"/>
+      <c r="BK133" s="3"/>
+      <c r="BL133" s="3"/>
+      <c r="BM133" s="3"/>
+      <c r="BN133" s="3"/>
+      <c r="BO133" s="3"/>
+      <c r="BP133" s="3"/>
+      <c r="BQ133" s="3"/>
+      <c r="BR133" s="3"/>
+      <c r="BS133" s="3"/>
+      <c r="BT133" s="3"/>
+      <c r="BU133" s="3"/>
+      <c r="BV133" s="3"/>
+      <c r="BW133" s="3"/>
+      <c r="BX133" s="3"/>
+      <c r="BY133" s="3"/>
+      <c r="BZ133" s="3"/>
+      <c r="CA133" s="3"/>
+      <c r="CB133" s="3"/>
+      <c r="CC133" s="3"/>
+      <c r="CD133" s="3"/>
+      <c r="CE133" s="3"/>
+      <c r="CF133" s="3"/>
+      <c r="CG133" s="3"/>
+      <c r="CH133" s="3"/>
+      <c r="CI133" s="3"/>
+      <c r="CJ133" s="3"/>
+    </row>
+    <row r="134" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1"/>
+      <c r="N134" s="1"/>
+      <c r="O134" s="1"/>
+      <c r="P134" s="1"/>
+      <c r="Q134" s="1"/>
+      <c r="R134" s="1"/>
+      <c r="S134" s="1"/>
+      <c r="T134" s="1"/>
+      <c r="U134" s="1"/>
+      <c r="V134" s="1"/>
+      <c r="W134" s="1"/>
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
+      <c r="Z134" s="1"/>
+      <c r="AA134" s="1"/>
+      <c r="AB134" s="1"/>
+      <c r="AC134" s="1"/>
+      <c r="AD134" s="1"/>
+      <c r="AE134" s="1"/>
+      <c r="AF134" s="1"/>
+      <c r="AG134" s="1"/>
+      <c r="AH134" s="1"/>
+      <c r="AI134" s="1"/>
+      <c r="AJ134" s="1"/>
+      <c r="AK134" s="1"/>
+      <c r="AL134" s="1"/>
+      <c r="AM134" s="1"/>
+      <c r="AN134" s="1"/>
+      <c r="AO134" s="1"/>
+      <c r="AP134" s="1"/>
+      <c r="AQ134" s="1"/>
+      <c r="AR134" s="1"/>
+      <c r="AS134" s="1"/>
+      <c r="AT134" s="1"/>
+      <c r="AU134" s="1"/>
+      <c r="AV134" s="1"/>
+      <c r="AW134" s="1"/>
+    </row>
+    <row r="135" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B135" s="4" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
         <v>317</v>
       </c>
@@ -6413,16 +6450,24 @@
         <v>318</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="8" t="s">
         <v>320</v>
       </c>
     </row>
+    <row r="138" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T136"/>
+  <autoFilter ref="A2:T137"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
